--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.42956800696399</v>
+        <v>11.60730480113165</v>
       </c>
       <c r="D2" t="n">
-        <v>71.5459545996804</v>
+        <v>11.62621762244807</v>
       </c>
       <c r="E2" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F2" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.04632008064509</v>
+        <v>7.157527013104827</v>
       </c>
       <c r="D3" t="n">
-        <v>44.24608444727114</v>
+        <v>7.18998872268156</v>
       </c>
       <c r="E3" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F3" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.78600528658792</v>
+        <v>9.390225859070538</v>
       </c>
       <c r="D4" t="n">
-        <v>57.61090028051955</v>
+        <v>9.361771295584427</v>
       </c>
       <c r="E4" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F4" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.47544335110791</v>
+        <v>9.664759544555036</v>
       </c>
       <c r="D5" t="n">
-        <v>59.49385982482814</v>
+        <v>9.667752221534574</v>
       </c>
       <c r="E5" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F5" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>81.82580053817047</v>
+        <v>13.2966925874527</v>
       </c>
       <c r="D6" t="n">
-        <v>81.67505263615382</v>
+        <v>13.272196053375</v>
       </c>
       <c r="E6" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F6" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.31200330116248</v>
+        <v>10.9382005364389</v>
       </c>
       <c r="D7" t="n">
-        <v>67.35428578220267</v>
+        <v>10.94507143960793</v>
       </c>
       <c r="E7" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F7" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.10760696997176</v>
+        <v>10.57998613262041</v>
       </c>
       <c r="D8" t="n">
-        <v>65.06208500632003</v>
+        <v>10.57258881352701</v>
       </c>
       <c r="E8" t="n">
-        <v>10.96905166636201</v>
+        <v>1.782470895783826</v>
       </c>
       <c r="F8" t="n">
-        <v>10.90822105709032</v>
+        <v>1.772585921777176</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
